--- a/results/q4_output/未来三年扩展规划.xlsx
+++ b/results/q4_output/未来三年扩展规划.xlsx
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1498</v>
+        <v>2086</v>
       </c>
       <c r="F2" t="n">
         <v>13885</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9106</v>
+        <v>0.9121</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1411</v>
+        <v>1936</v>
       </c>
       <c r="F3" t="n">
         <v>12828</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9497</v>
+        <v>0.9505</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1374</v>
+        <v>1884</v>
       </c>
       <c r="F4" t="n">
         <v>10805</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7493</v>
+        <v>0.7536</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1349</v>
+        <v>1657</v>
       </c>
       <c r="F5" t="n">
         <v>11954</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7638</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -684,13 +684,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1299</v>
+        <v>1351</v>
       </c>
       <c r="F6" t="n">
         <v>8299</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8197</v>
+        <v>0.8228</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1283</v>
+        <v>1062</v>
       </c>
       <c r="F7" t="n">
         <v>10391</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6952</v>
+        <v>0.7007</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -772,13 +772,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1035</v>
+        <v>503</v>
       </c>
       <c r="F8" t="n">
         <v>4966</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8996</v>
+        <v>0.9014</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>772</v>
+        <v>488</v>
       </c>
       <c r="F9" t="n">
         <v>6437</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8711</v>
+        <v>0.8733</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>685</v>
+        <v>143</v>
       </c>
       <c r="F10" t="n">
         <v>4414</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7743</v>
+        <v>0.7785</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>626</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
         <v>5931</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7577</v>
+        <v>0.7621</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1648</v>
+        <v>2295</v>
       </c>
       <c r="F12" t="n">
         <v>13885</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9106</v>
+        <v>0.9121</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -992,13 +992,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1552</v>
+        <v>2130</v>
       </c>
       <c r="F13" t="n">
         <v>12828</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9497</v>
+        <v>0.9505</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1511</v>
+        <v>2072</v>
       </c>
       <c r="F14" t="n">
         <v>10805</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7492</v>
+        <v>0.7536</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1483</v>
+        <v>1822</v>
       </c>
       <c r="F15" t="n">
         <v>11954</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7638</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1428</v>
+        <v>1486</v>
       </c>
       <c r="F16" t="n">
         <v>8299</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8197</v>
+        <v>0.8228</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1168,13 +1168,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1411</v>
+        <v>1169</v>
       </c>
       <c r="F17" t="n">
         <v>10391</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.7006</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1139</v>
+        <v>553</v>
       </c>
       <c r="F18" t="n">
         <v>4966</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8995</v>
+        <v>0.9014</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1256,13 +1256,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>849</v>
+        <v>537</v>
       </c>
       <c r="F19" t="n">
         <v>6437</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8711</v>
+        <v>0.8733</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1300,13 +1300,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>754</v>
+        <v>158</v>
       </c>
       <c r="F20" t="n">
         <v>4414</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7743</v>
+        <v>0.7785</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1344,13 +1344,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>689</v>
+        <v>33</v>
       </c>
       <c r="F21" t="n">
         <v>5931</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7577</v>
+        <v>0.7621</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1813</v>
+        <v>2524</v>
       </c>
       <c r="F22" t="n">
         <v>13885</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9448</v>
+        <v>0.9121</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1432,27 +1432,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1707</v>
+        <v>2343</v>
       </c>
       <c r="F23" t="n">
         <v>12828</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9617</v>
+        <v>0.9505</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L23" t="n">
         <v>82</v>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1663</v>
+        <v>2280</v>
       </c>
       <c r="F24" t="n">
         <v>10805</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8491</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1632</v>
+        <v>2004</v>
       </c>
       <c r="F25" t="n">
         <v>11954</v>
       </c>
       <c r="G25" t="n">
-        <v>0.856</v>
+        <v>0.7637</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1564,13 +1564,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1571</v>
+        <v>1634</v>
       </c>
       <c r="F26" t="n">
         <v>8299</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8903</v>
+        <v>0.8228</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1608,13 +1608,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1552</v>
+        <v>1286</v>
       </c>
       <c r="F27" t="n">
         <v>10391</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8174</v>
+        <v>0.7006</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1253</v>
+        <v>608</v>
       </c>
       <c r="F28" t="n">
         <v>4966</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9374</v>
+        <v>0.9014</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1696,13 +1696,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>934</v>
+        <v>591</v>
       </c>
       <c r="F29" t="n">
         <v>6437</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9224</v>
+        <v>0.8733</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>829</v>
+        <v>173</v>
       </c>
       <c r="F30" t="n">
         <v>4414</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8637</v>
+        <v>0.7784</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>758</v>
+        <v>36</v>
       </c>
       <c r="F31" t="n">
         <v>5931</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8551</v>
+        <v>0.7621</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1498</v>
+        <v>2086</v>
       </c>
       <c r="F32" t="n">
         <v>13885</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9106</v>
+        <v>0.9121</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1872,13 +1872,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1411</v>
+        <v>1936</v>
       </c>
       <c r="F33" t="n">
         <v>12828</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9497</v>
+        <v>0.9505</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1374</v>
+        <v>1884</v>
       </c>
       <c r="F34" t="n">
         <v>10805</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7493</v>
+        <v>0.7536</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1960,13 +1960,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1349</v>
+        <v>1657</v>
       </c>
       <c r="F35" t="n">
         <v>11954</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7638</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2004,13 +2004,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1299</v>
+        <v>1351</v>
       </c>
       <c r="F36" t="n">
         <v>8299</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8197</v>
+        <v>0.8228</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2048,13 +2048,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1283</v>
+        <v>1062</v>
       </c>
       <c r="F37" t="n">
         <v>10391</v>
       </c>
       <c r="G37" t="n">
-        <v>0.6952</v>
+        <v>0.7007</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2092,13 +2092,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1035</v>
+        <v>503</v>
       </c>
       <c r="F38" t="n">
         <v>4966</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8996</v>
+        <v>0.9014</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2136,13 +2136,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>772</v>
+        <v>488</v>
       </c>
       <c r="F39" t="n">
         <v>6437</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8711</v>
+        <v>0.8733</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>685</v>
+        <v>143</v>
       </c>
       <c r="F40" t="n">
         <v>4414</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7743</v>
+        <v>0.7785</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2224,13 +2224,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>626</v>
+        <v>30</v>
       </c>
       <c r="F41" t="n">
         <v>5931</v>
       </c>
       <c r="G41" t="n">
-        <v>0.7577</v>
+        <v>0.7621</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1723</v>
+        <v>2399</v>
       </c>
       <c r="F42" t="n">
         <v>13885</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9106</v>
+        <v>0.9121</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1622</v>
+        <v>2227</v>
       </c>
       <c r="F43" t="n">
         <v>12828</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9497</v>
+        <v>0.9505</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2356,13 +2356,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1580</v>
+        <v>2167</v>
       </c>
       <c r="F44" t="n">
         <v>10805</v>
       </c>
       <c r="G44" t="n">
-        <v>0.7492</v>
+        <v>0.7536</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2400,13 +2400,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1551</v>
+        <v>1905</v>
       </c>
       <c r="F45" t="n">
         <v>11954</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7637</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1493</v>
+        <v>1553</v>
       </c>
       <c r="F46" t="n">
         <v>8299</v>
       </c>
       <c r="G46" t="n">
-        <v>0.8197</v>
+        <v>0.8228</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1475</v>
+        <v>1222</v>
       </c>
       <c r="F47" t="n">
         <v>10391</v>
       </c>
       <c r="G47" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.7006</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2532,13 +2532,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1191</v>
+        <v>578</v>
       </c>
       <c r="F48" t="n">
         <v>4966</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8995</v>
+        <v>0.9014</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2576,13 +2576,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>888</v>
+        <v>562</v>
       </c>
       <c r="F49" t="n">
         <v>6437</v>
       </c>
       <c r="G49" t="n">
-        <v>0.871</v>
+        <v>0.8733</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2620,13 +2620,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>788</v>
+        <v>165</v>
       </c>
       <c r="F50" t="n">
         <v>4414</v>
       </c>
       <c r="G50" t="n">
-        <v>0.7743</v>
+        <v>0.7785</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2664,13 +2664,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>720</v>
+        <v>34</v>
       </c>
       <c r="F51" t="n">
         <v>5931</v>
       </c>
       <c r="G51" t="n">
-        <v>0.7577</v>
+        <v>0.7621</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1981</v>
+        <v>2759</v>
       </c>
       <c r="F52" t="n">
         <v>13885</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9486</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2752,27 +2752,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1865</v>
+        <v>2560</v>
       </c>
       <c r="F53" t="n">
         <v>12828</v>
       </c>
       <c r="G53" t="n">
-        <v>0.9117</v>
+        <v>0.9696</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="L53" t="n">
         <v>82</v>
@@ -2796,27 +2796,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1817</v>
+        <v>2491</v>
       </c>
       <c r="F54" t="n">
         <v>10805</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8858</v>
+        <v>0.8487</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L54" t="n">
         <v>66</v>
@@ -2840,27 +2840,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1784</v>
+        <v>2191</v>
       </c>
       <c r="F55" t="n">
         <v>11954</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.8548</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L55" t="n">
         <v>84</v>
@@ -2884,13 +2884,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1717</v>
+        <v>1786</v>
       </c>
       <c r="F56" t="n">
         <v>8299</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9162</v>
+        <v>0.8984</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2928,27 +2928,27 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1696</v>
+        <v>1405</v>
       </c>
       <c r="F57" t="n">
         <v>10391</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8595</v>
+        <v>0.8325</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L57" t="n">
         <v>64</v>
@@ -2972,13 +2972,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1369</v>
+        <v>665</v>
       </c>
       <c r="F58" t="n">
         <v>4966</v>
       </c>
       <c r="G58" t="n">
-        <v>0.951</v>
+        <v>0.9439</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3016,13 +3016,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1021</v>
+        <v>646</v>
       </c>
       <c r="F59" t="n">
         <v>6437</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9412</v>
+        <v>0.9281</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -3060,13 +3060,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>906</v>
+        <v>189</v>
       </c>
       <c r="F60" t="n">
         <v>4414</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8966</v>
+        <v>0.8764</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3104,13 +3104,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>828</v>
+        <v>39</v>
       </c>
       <c r="F61" t="n">
         <v>5931</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8911</v>
+        <v>0.8678</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3148,13 +3148,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1498</v>
+        <v>2086</v>
       </c>
       <c r="F62" t="n">
         <v>13885</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9106</v>
+        <v>0.9121</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1411</v>
+        <v>1936</v>
       </c>
       <c r="F63" t="n">
         <v>12828</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9497</v>
+        <v>0.9505</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3236,13 +3236,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1374</v>
+        <v>1884</v>
       </c>
       <c r="F64" t="n">
         <v>10805</v>
       </c>
       <c r="G64" t="n">
-        <v>0.7493</v>
+        <v>0.7536</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3280,13 +3280,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1349</v>
+        <v>1657</v>
       </c>
       <c r="F65" t="n">
         <v>11954</v>
       </c>
       <c r="G65" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7638</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3324,13 +3324,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1299</v>
+        <v>1351</v>
       </c>
       <c r="F66" t="n">
         <v>8299</v>
       </c>
       <c r="G66" t="n">
-        <v>0.8197</v>
+        <v>0.8228</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1283</v>
+        <v>1062</v>
       </c>
       <c r="F67" t="n">
         <v>10391</v>
       </c>
       <c r="G67" t="n">
-        <v>0.6952</v>
+        <v>0.7007</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3412,13 +3412,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1035</v>
+        <v>503</v>
       </c>
       <c r="F68" t="n">
         <v>4966</v>
       </c>
       <c r="G68" t="n">
-        <v>0.8996</v>
+        <v>0.9014</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3456,13 +3456,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>772</v>
+        <v>488</v>
       </c>
       <c r="F69" t="n">
         <v>6437</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8711</v>
+        <v>0.8733</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3500,13 +3500,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>685</v>
+        <v>143</v>
       </c>
       <c r="F70" t="n">
         <v>4414</v>
       </c>
       <c r="G70" t="n">
-        <v>0.7743</v>
+        <v>0.7785</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>626</v>
+        <v>30</v>
       </c>
       <c r="F71" t="n">
         <v>5931</v>
       </c>
       <c r="G71" t="n">
-        <v>0.7577</v>
+        <v>0.7621</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3588,13 +3588,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1798</v>
+        <v>2504</v>
       </c>
       <c r="F72" t="n">
         <v>13885</v>
       </c>
       <c r="G72" t="n">
-        <v>0.9224</v>
+        <v>0.9121</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3632,27 +3632,27 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1693</v>
+        <v>2323</v>
       </c>
       <c r="F73" t="n">
         <v>12828</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9549</v>
+        <v>0.9505</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L73" t="n">
         <v>82</v>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1649</v>
+        <v>2261</v>
       </c>
       <c r="F74" t="n">
         <v>10805</v>
       </c>
       <c r="G74" t="n">
-        <v>0.7837</v>
+        <v>0.7536</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3720,13 +3720,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1618</v>
+        <v>1988</v>
       </c>
       <c r="F75" t="n">
         <v>11954</v>
       </c>
       <c r="G75" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7637</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3764,13 +3764,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1558</v>
+        <v>1621</v>
       </c>
       <c r="F76" t="n">
         <v>8299</v>
       </c>
       <c r="G76" t="n">
-        <v>0.844</v>
+        <v>0.8228</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3808,13 +3808,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1539</v>
+        <v>1275</v>
       </c>
       <c r="F77" t="n">
         <v>10391</v>
       </c>
       <c r="G77" t="n">
-        <v>0.7373</v>
+        <v>0.7006</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3852,13 +3852,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1242</v>
+        <v>603</v>
       </c>
       <c r="F78" t="n">
         <v>4966</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9126</v>
+        <v>0.9014</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3896,13 +3896,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>926</v>
+        <v>586</v>
       </c>
       <c r="F79" t="n">
         <v>6437</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8887</v>
+        <v>0.8733</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3940,13 +3940,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>822</v>
+        <v>172</v>
       </c>
       <c r="F80" t="n">
         <v>4414</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8051</v>
+        <v>0.7784</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3984,13 +3984,13 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>752</v>
+        <v>35</v>
       </c>
       <c r="F81" t="n">
         <v>5931</v>
       </c>
       <c r="G81" t="n">
-        <v>0.7913</v>
+        <v>0.7621</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -4028,27 +4028,27 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2157</v>
+        <v>3004</v>
       </c>
       <c r="F82" t="n">
         <v>13885</v>
       </c>
       <c r="G82" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.9569</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L82" t="n">
         <v>88</v>
@@ -4072,27 +4072,27 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2031</v>
+        <v>2788</v>
       </c>
       <c r="F83" t="n">
-        <v>12920</v>
+        <v>12828</v>
       </c>
       <c r="G83" t="n">
-        <v>0.8565</v>
+        <v>0.9738</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="L83" t="n">
         <v>82</v>
@@ -4116,13 +4116,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1979</v>
+        <v>2713</v>
       </c>
       <c r="F84" t="n">
         <v>10805</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9195</v>
+        <v>0.8189</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -4130,13 +4130,13 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L84" t="n">
         <v>66</v>
@@ -4160,27 +4160,27 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1942</v>
+        <v>2385</v>
       </c>
       <c r="F85" t="n">
         <v>11954</v>
       </c>
       <c r="G85" t="n">
-        <v>0.9308</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L85" t="n">
         <v>84</v>
@@ -4204,13 +4204,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1870</v>
+        <v>1945</v>
       </c>
       <c r="F86" t="n">
         <v>8299</v>
       </c>
       <c r="G86" t="n">
-        <v>0.9366</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -4248,27 +4248,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1847</v>
+        <v>1530</v>
       </c>
       <c r="F87" t="n">
         <v>10391</v>
       </c>
       <c r="G87" t="n">
-        <v>0.8773</v>
+        <v>0.8633</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L87" t="n">
         <v>64</v>
@@ -4292,13 +4292,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1491</v>
+        <v>724</v>
       </c>
       <c r="F88" t="n">
         <v>4966</v>
       </c>
       <c r="G88" t="n">
-        <v>0.9776</v>
+        <v>0.9537</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4336,13 +4336,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1111</v>
+        <v>703</v>
       </c>
       <c r="F89" t="n">
         <v>6437</v>
       </c>
       <c r="G89" t="n">
-        <v>0.9557</v>
+        <v>0.9408</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4380,13 +4380,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>986</v>
+        <v>206</v>
       </c>
       <c r="F90" t="n">
         <v>4414</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9565</v>
+        <v>0.8993</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4424,13 +4424,13 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>902</v>
+        <v>43</v>
       </c>
       <c r="F91" t="n">
         <v>5931</v>
       </c>
       <c r="G91" t="n">
-        <v>0.9555</v>
+        <v>0.8925</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>

--- a/results/q4_output/未来三年扩展规划.xlsx
+++ b/results/q4_output/未来三年扩展规划.xlsx
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2086</v>
+        <v>1417</v>
       </c>
       <c r="F2" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9121</v>
+        <v>0.9411</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         <v>129</v>
       </c>
       <c r="L2" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1936</v>
+        <v>1302</v>
       </c>
       <c r="F3" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9505</v>
+        <v>0.9326</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         <v>119</v>
       </c>
       <c r="L3" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1884</v>
+        <v>1026</v>
       </c>
       <c r="F4" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7536</v>
+        <v>0.9458</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L4" t="n">
         <v>66</v>
@@ -636,17 +636,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1657</v>
+        <v>1470</v>
       </c>
       <c r="F5" t="n">
         <v>11954</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7638</v>
+        <v>0.8616</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L5" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -680,17 +680,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1351</v>
+        <v>1326</v>
       </c>
       <c r="F6" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8228</v>
+        <v>0.9019</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>76</v>
       </c>
       <c r="L6" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1062</v>
+        <v>1311</v>
       </c>
       <c r="F7" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7007</v>
+        <v>0.9609</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L7" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -768,17 +768,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>503</v>
+        <v>632</v>
       </c>
       <c r="F8" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9014</v>
+        <v>0.8224</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -812,34 +812,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>488</v>
+        <v>649</v>
       </c>
       <c r="F9" t="n">
-        <v>6437</v>
+        <v>8069</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8733</v>
+        <v>0.6679</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
         <v>59</v>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
@@ -856,17 +856,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>143</v>
+        <v>1448</v>
       </c>
       <c r="F10" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7785</v>
+        <v>0.9065</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -880,10 +880,10 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -900,34 +900,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>775</v>
       </c>
       <c r="F11" t="n">
-        <v>5931</v>
+        <v>7586</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7621</v>
+        <v>0.6219</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
         <v>54</v>
       </c>
       <c r="L11" t="n">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12">
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2295</v>
+        <v>1559</v>
       </c>
       <c r="F12" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9121</v>
+        <v>0.9417</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>129</v>
       </c>
       <c r="L12" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
@@ -992,13 +992,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2130</v>
+        <v>1432</v>
       </c>
       <c r="F13" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9505</v>
+        <v>0.9332</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>119</v>
       </c>
       <c r="L13" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14">
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2072</v>
+        <v>1129</v>
       </c>
       <c r="F14" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7536</v>
+        <v>0.9463</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L14" t="n">
         <v>66</v>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1822</v>
+        <v>1616</v>
       </c>
       <c r="F15" t="n">
         <v>11954</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7638</v>
+        <v>0.8647</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1100,10 +1100,10 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L15" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1120,17 +1120,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1486</v>
+        <v>1459</v>
       </c>
       <c r="F16" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8228</v>
+        <v>0.9051</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>76</v>
       </c>
       <c r="L16" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -1168,13 +1168,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1169</v>
+        <v>1442</v>
       </c>
       <c r="F17" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7006</v>
+        <v>0.9617</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L17" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
@@ -1208,17 +1208,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>553</v>
+        <v>695</v>
       </c>
       <c r="F18" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9014</v>
+        <v>0.8285</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1232,10 +1232,10 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L18" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
@@ -1252,34 +1252,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>537</v>
+        <v>714</v>
       </c>
       <c r="F19" t="n">
-        <v>6437</v>
+        <v>8184</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8733</v>
+        <v>0.6585</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K19" t="n">
         <v>59</v>
       </c>
       <c r="L19" t="n">
-        <v>44</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>158</v>
+        <v>1593</v>
       </c>
       <c r="F20" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7785</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
@@ -1340,34 +1340,34 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33</v>
+        <v>852</v>
       </c>
       <c r="F21" t="n">
-        <v>5931</v>
+        <v>7701</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7621</v>
+        <v>0.614</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
         <v>54</v>
       </c>
       <c r="L21" t="n">
-        <v>42</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22">
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2524</v>
+        <v>1715</v>
       </c>
       <c r="F22" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9121</v>
+        <v>0.9545</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>129</v>
       </c>
       <c r="L22" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2343</v>
+        <v>1575</v>
       </c>
       <c r="F23" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9505</v>
+        <v>0.9482</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>119</v>
       </c>
       <c r="L23" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2280</v>
+        <v>1242</v>
       </c>
       <c r="F24" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L24" t="n">
         <v>66</v>
@@ -1516,17 +1516,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2004</v>
+        <v>1778</v>
       </c>
       <c r="F25" t="n">
         <v>11954</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7637</v>
+        <v>0.898</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L25" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26">
@@ -1560,17 +1560,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1634</v>
+        <v>1605</v>
       </c>
       <c r="F26" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8228</v>
+        <v>0.9281</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>76</v>
       </c>
       <c r="L26" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27">
@@ -1608,13 +1608,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1286</v>
+        <v>1586</v>
       </c>
       <c r="F27" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7006</v>
+        <v>0.9702</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L27" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>608</v>
+        <v>765</v>
       </c>
       <c r="F28" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9014</v>
+        <v>0.873</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
@@ -1692,17 +1692,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>591</v>
+        <v>785</v>
       </c>
       <c r="F29" t="n">
-        <v>6437</v>
+        <v>8299</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8733</v>
+        <v>0.7328</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>59</v>
       </c>
       <c r="L29" t="n">
-        <v>44</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30">
@@ -1736,34 +1736,34 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>173</v>
+        <v>1752</v>
       </c>
       <c r="F30" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7784</v>
+        <v>0.892</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L30" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31">
@@ -1780,34 +1780,34 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>36</v>
+        <v>937</v>
       </c>
       <c r="F31" t="n">
-        <v>5931</v>
+        <v>7816</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7621</v>
+        <v>0.7</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
         <v>54</v>
       </c>
       <c r="L31" t="n">
-        <v>42</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32">
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2086</v>
+        <v>1417</v>
       </c>
       <c r="F32" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9121</v>
+        <v>0.9411</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>129</v>
       </c>
       <c r="L32" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33">
@@ -1872,13 +1872,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1936</v>
+        <v>1302</v>
       </c>
       <c r="F33" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9505</v>
+        <v>0.9326</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>119</v>
       </c>
       <c r="L33" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34">
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1884</v>
+        <v>1026</v>
       </c>
       <c r="F34" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7536</v>
+        <v>0.9458</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L34" t="n">
         <v>66</v>
@@ -1956,17 +1956,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1657</v>
+        <v>1470</v>
       </c>
       <c r="F35" t="n">
         <v>11954</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7638</v>
+        <v>0.8616</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L35" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36">
@@ -2000,17 +2000,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1351</v>
+        <v>1326</v>
       </c>
       <c r="F36" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8228</v>
+        <v>0.9019</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>76</v>
       </c>
       <c r="L36" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37">
@@ -2048,13 +2048,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1062</v>
+        <v>1311</v>
       </c>
       <c r="F37" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7007</v>
+        <v>0.9609</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L37" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38">
@@ -2088,17 +2088,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>503</v>
+        <v>632</v>
       </c>
       <c r="F38" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9014</v>
+        <v>0.8224</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L38" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39">
@@ -2132,34 +2132,34 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>488</v>
+        <v>649</v>
       </c>
       <c r="F39" t="n">
-        <v>6437</v>
+        <v>8069</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8733</v>
+        <v>0.6679</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K39" t="n">
         <v>59</v>
       </c>
       <c r="L39" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40">
@@ -2176,17 +2176,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>143</v>
+        <v>1448</v>
       </c>
       <c r="F40" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7785</v>
+        <v>0.9065</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L40" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41">
@@ -2220,34 +2220,34 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>30</v>
+        <v>775</v>
       </c>
       <c r="F41" t="n">
-        <v>5931</v>
+        <v>7586</v>
       </c>
       <c r="G41" t="n">
-        <v>0.7621</v>
+        <v>0.6219</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K41" t="n">
         <v>54</v>
       </c>
       <c r="L41" t="n">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42">
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2399</v>
+        <v>1630</v>
       </c>
       <c r="F42" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9121</v>
+        <v>0.9514</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>129</v>
       </c>
       <c r="L42" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43">
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2227</v>
+        <v>1497</v>
       </c>
       <c r="F43" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9505</v>
+        <v>0.9445</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>119</v>
       </c>
       <c r="L43" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44">
@@ -2356,13 +2356,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2167</v>
+        <v>1180</v>
       </c>
       <c r="F44" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G44" t="n">
-        <v>0.7536</v>
+        <v>0.9553</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L44" t="n">
         <v>66</v>
@@ -2396,17 +2396,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1905</v>
+        <v>1690</v>
       </c>
       <c r="F45" t="n">
         <v>11954</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7637</v>
+        <v>0.889</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2420,10 +2420,10 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L45" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1553</v>
+        <v>1525</v>
       </c>
       <c r="F46" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G46" t="n">
-        <v>0.8228</v>
+        <v>0.9212</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>76</v>
       </c>
       <c r="L46" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47">
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1222</v>
+        <v>1508</v>
       </c>
       <c r="F47" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G47" t="n">
-        <v>0.7006</v>
+        <v>0.9678</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L47" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>578</v>
+        <v>727</v>
       </c>
       <c r="F48" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9014</v>
+        <v>0.8597</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2552,10 +2552,10 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L48" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49">
@@ -2572,17 +2572,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>562</v>
+        <v>746</v>
       </c>
       <c r="F49" t="n">
-        <v>6437</v>
+        <v>8184</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8733</v>
+        <v>0.7214</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>59</v>
       </c>
       <c r="L49" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50">
@@ -2616,34 +2616,34 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>165</v>
+        <v>1665</v>
       </c>
       <c r="F50" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
       <c r="G50" t="n">
-        <v>0.7785</v>
+        <v>0.9133</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L50" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51">
@@ -2660,34 +2660,34 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>34</v>
+        <v>891</v>
       </c>
       <c r="F51" t="n">
-        <v>5931</v>
+        <v>7701</v>
       </c>
       <c r="G51" t="n">
-        <v>0.7621</v>
+        <v>0.6851</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K51" t="n">
         <v>54</v>
       </c>
       <c r="L51" t="n">
-        <v>42</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52">
@@ -2708,30 +2708,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2759</v>
+        <v>1874</v>
       </c>
       <c r="F52" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9486</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K52" t="n">
         <v>129</v>
       </c>
       <c r="L52" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53">
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2560</v>
+        <v>1721</v>
       </c>
       <c r="F53" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G53" t="n">
-        <v>0.9696</v>
+        <v>0.9449</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>119</v>
       </c>
       <c r="L53" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54">
@@ -2796,27 +2796,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2491</v>
+        <v>1357</v>
       </c>
       <c r="F54" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8487</v>
+        <v>0.9555</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L54" t="n">
         <v>66</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2191</v>
+        <v>1943</v>
       </c>
       <c r="F55" t="n">
         <v>11954</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8548</v>
+        <v>0.8952</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>110</v>
       </c>
       <c r="L55" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56">
@@ -2880,17 +2880,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1786</v>
+        <v>1754</v>
       </c>
       <c r="F56" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8984</v>
+        <v>0.9291</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>76</v>
       </c>
       <c r="L56" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57">
@@ -2928,13 +2928,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1405</v>
+        <v>1734</v>
       </c>
       <c r="F57" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8325</v>
+        <v>0.9695</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2948,10 +2948,10 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L57" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58">
@@ -2968,17 +2968,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>665</v>
+        <v>836</v>
       </c>
       <c r="F58" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9439</v>
+        <v>0.8752</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2992,10 +2992,10 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L58" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59">
@@ -3012,17 +3012,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>646</v>
+        <v>858</v>
       </c>
       <c r="F59" t="n">
-        <v>6437</v>
+        <v>8184</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9281</v>
+        <v>0.7527</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>59</v>
       </c>
       <c r="L59" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
     </row>
     <row r="60">
@@ -3056,34 +3056,34 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>189</v>
+        <v>1915</v>
       </c>
       <c r="F60" t="n">
         <v>4414</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8764</v>
+        <v>0.8269</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K60" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L60" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61">
@@ -3100,34 +3100,34 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>39</v>
+        <v>1025</v>
       </c>
       <c r="F61" t="n">
-        <v>5931</v>
+        <v>7816</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8678</v>
+        <v>0.7053</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K61" t="n">
         <v>54</v>
       </c>
       <c r="L61" t="n">
-        <v>42</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62">
@@ -3148,13 +3148,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2086</v>
+        <v>1417</v>
       </c>
       <c r="F62" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9121</v>
+        <v>0.9411</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>129</v>
       </c>
       <c r="L62" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1936</v>
+        <v>1302</v>
       </c>
       <c r="F63" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9505</v>
+        <v>0.9326</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>119</v>
       </c>
       <c r="L63" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64">
@@ -3236,13 +3236,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1884</v>
+        <v>1026</v>
       </c>
       <c r="F64" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G64" t="n">
-        <v>0.7536</v>
+        <v>0.9458</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L64" t="n">
         <v>66</v>
@@ -3276,17 +3276,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1657</v>
+        <v>1470</v>
       </c>
       <c r="F65" t="n">
         <v>11954</v>
       </c>
       <c r="G65" t="n">
-        <v>0.7638</v>
+        <v>0.8616</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3300,10 +3300,10 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L65" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66">
@@ -3320,17 +3320,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1351</v>
+        <v>1326</v>
       </c>
       <c r="F66" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G66" t="n">
-        <v>0.8228</v>
+        <v>0.9019</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>76</v>
       </c>
       <c r="L66" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1062</v>
+        <v>1311</v>
       </c>
       <c r="F67" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G67" t="n">
-        <v>0.7007</v>
+        <v>0.9609</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3388,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L67" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>503</v>
+        <v>632</v>
       </c>
       <c r="F68" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9014</v>
+        <v>0.8224</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L68" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69">
@@ -3452,34 +3452,34 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>488</v>
+        <v>649</v>
       </c>
       <c r="F69" t="n">
-        <v>6437</v>
+        <v>8069</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8733</v>
+        <v>0.6679</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K69" t="n">
         <v>59</v>
       </c>
       <c r="L69" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
     </row>
     <row r="70">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>143</v>
+        <v>1448</v>
       </c>
       <c r="F70" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
       <c r="G70" t="n">
-        <v>0.7785</v>
+        <v>0.9065</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L70" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71">
@@ -3540,34 +3540,34 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>30</v>
+        <v>775</v>
       </c>
       <c r="F71" t="n">
-        <v>5931</v>
+        <v>7586</v>
       </c>
       <c r="G71" t="n">
-        <v>0.7621</v>
+        <v>0.6219</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K71" t="n">
         <v>54</v>
       </c>
       <c r="L71" t="n">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="72">
@@ -3588,13 +3588,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2504</v>
+        <v>1701</v>
       </c>
       <c r="F72" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G72" t="n">
-        <v>0.9121</v>
+        <v>0.9539</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>129</v>
       </c>
       <c r="L72" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="73">
@@ -3632,13 +3632,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2323</v>
+        <v>1562</v>
       </c>
       <c r="F73" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9505</v>
+        <v>0.9475</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>119</v>
       </c>
       <c r="L73" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74">
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2261</v>
+        <v>1231</v>
       </c>
       <c r="F74" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G74" t="n">
-        <v>0.7536</v>
+        <v>0.9577</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L74" t="n">
         <v>66</v>
@@ -3716,17 +3716,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1988</v>
+        <v>1763</v>
       </c>
       <c r="F75" t="n">
         <v>11954</v>
       </c>
       <c r="G75" t="n">
-        <v>0.7637</v>
+        <v>0.8956</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3740,10 +3740,10 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L75" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76">
@@ -3760,17 +3760,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1621</v>
+        <v>1592</v>
       </c>
       <c r="F76" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8228</v>
+        <v>0.9256</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>76</v>
       </c>
       <c r="L76" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77">
@@ -3808,13 +3808,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1275</v>
+        <v>1573</v>
       </c>
       <c r="F77" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G77" t="n">
-        <v>0.7006</v>
+        <v>0.9694</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3828,10 +3828,10 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L77" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78">
@@ -3848,17 +3848,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>603</v>
+        <v>758</v>
       </c>
       <c r="F78" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9014</v>
+        <v>0.8683</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3872,10 +3872,10 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L78" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79">
@@ -3892,17 +3892,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>586</v>
+        <v>779</v>
       </c>
       <c r="F79" t="n">
-        <v>6437</v>
+        <v>8184</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8733</v>
+        <v>0.7389</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>59</v>
       </c>
       <c r="L79" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
     </row>
     <row r="80">
@@ -3936,34 +3936,34 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>172</v>
+        <v>1738</v>
       </c>
       <c r="F80" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
       <c r="G80" t="n">
-        <v>0.7784</v>
+        <v>0.895</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K80" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L80" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="81">
@@ -3980,34 +3980,34 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>35</v>
+        <v>930</v>
       </c>
       <c r="F81" t="n">
-        <v>5931</v>
+        <v>7701</v>
       </c>
       <c r="G81" t="n">
-        <v>0.7621</v>
+        <v>0.7048</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K81" t="n">
         <v>54</v>
       </c>
       <c r="L81" t="n">
-        <v>42</v>
+        <v>124</v>
       </c>
     </row>
     <row r="82">
@@ -4028,30 +4028,30 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3004</v>
+        <v>2041</v>
       </c>
       <c r="F82" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G82" t="n">
-        <v>0.9569</v>
+        <v>0.883</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K82" t="n">
         <v>129</v>
       </c>
       <c r="L82" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83">
@@ -4072,30 +4072,30 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2788</v>
+        <v>1874</v>
       </c>
       <c r="F83" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G83" t="n">
-        <v>0.9738</v>
+        <v>0.9171</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K83" t="n">
         <v>119</v>
       </c>
       <c r="L83" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84">
@@ -4116,27 +4116,27 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2713</v>
+        <v>1478</v>
       </c>
       <c r="F84" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G84" t="n">
-        <v>0.8189</v>
+        <v>0.9515</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="L84" t="n">
         <v>66</v>
@@ -4156,34 +4156,34 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2385</v>
+        <v>2116</v>
       </c>
       <c r="F85" t="n">
         <v>11954</v>
       </c>
       <c r="G85" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.8852</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L85" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86">
@@ -4200,34 +4200,34 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1945</v>
+        <v>1910</v>
       </c>
       <c r="F86" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G86" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K86" t="n">
         <v>76</v>
       </c>
       <c r="L86" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
     </row>
     <row r="87">
@@ -4248,13 +4248,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1530</v>
+        <v>1888</v>
       </c>
       <c r="F87" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G87" t="n">
-        <v>0.8633</v>
+        <v>0.9669</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L87" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88">
@@ -4288,17 +4288,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>724</v>
+        <v>910</v>
       </c>
       <c r="F88" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G88" t="n">
-        <v>0.9537</v>
+        <v>0.863</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4312,10 +4312,10 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L88" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="89">
@@ -4332,17 +4332,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>703</v>
+        <v>935</v>
       </c>
       <c r="F89" t="n">
-        <v>6437</v>
+        <v>8184</v>
       </c>
       <c r="G89" t="n">
-        <v>0.9408</v>
+        <v>0.7284</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>59</v>
       </c>
       <c r="L89" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
     </row>
     <row r="90">
@@ -4376,34 +4376,34 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>206</v>
+        <v>2085</v>
       </c>
       <c r="F90" t="n">
         <v>4414</v>
       </c>
       <c r="G90" t="n">
-        <v>0.8993</v>
+        <v>0.784</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K90" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L90" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="91">
@@ -4420,34 +4420,34 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>43</v>
+        <v>1116</v>
       </c>
       <c r="F91" t="n">
-        <v>5931</v>
+        <v>7816</v>
       </c>
       <c r="G91" t="n">
-        <v>0.8925</v>
+        <v>0.6763</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K91" t="n">
         <v>54</v>
       </c>
       <c r="L91" t="n">
-        <v>42</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
